--- a/Collaudo/Inventario_di_prova_con_difetti.xlsx
+++ b/Collaudo/Inventario_di_prova_con_difetti.xlsx
@@ -433,19 +433,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,40 +462,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Asset Function</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Modello/Descrizione</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Numero di serie</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>IMEI</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Costo</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Fornitore</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Centro di costo</t>
         </is>
@@ -518,36 +524,37 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>riga regolare</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Disponibile</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Lenovo ThinkPad T14 Gen 5</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>PF4BAU01</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
         <v>1200</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Dell Italia</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>CC-01</t>
         </is>
@@ -564,32 +571,33 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>senza modello</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Disponibile</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>PF4BAU02</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
         <v>1150</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Dell Italia</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>CC-01</t>
         </is>
@@ -614,32 +622,37 @@
           <t>Tablet</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ricondizionato</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Controllare</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Dell Latitude 7320 Detachable</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>8HK903</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
         <v>900</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Dell Italia</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>CC-02</t>
         </is>
@@ -652,28 +665,29 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>verra' scartata</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
         <is>
           <t>senza identificativo</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
         <v>800</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Dell Italia</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>CC-02</t>
         </is>
@@ -686,32 +700,33 @@
           <t>Iphone</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>verra' ignorato</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Apple iPhone 14</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>356938035643809</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>1000</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>CC-03</t>
         </is>
@@ -719,8 +734,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
